--- a/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
+++ b/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
@@ -20,7 +20,7 @@
     <t>AT32F415RBT7_WorkBench</t>
   </si>
   <si>
-    <t>lto-llvm-475aad.o</t>
+    <t>lto-llvm-b7239f.o</t>
   </si>
   <si>
     <t>startup_at32f415.o</t>
@@ -249,7 +249,7 @@
               <c:strCache>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-475aad.o</c:v>
+                  <c:v>lto-llvm-b7239f.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>startup_at32f415.o</c:v>
@@ -344,7 +344,7 @@
               <c:strCache>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-475aad.o</c:v>
+                  <c:v>lto-llvm-b7239f.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>mf_w.l</c:v>
@@ -464,112 +464,112 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>95.647705078125</c:v>
+                  <c:v>95.65001678466797</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.791911602020264</c:v>
+                  <c:v>1.790960192680359</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.3576740622520447</c:v>
+                  <c:v>0.3574841618537903</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.2957008183002472</c:v>
+                  <c:v>0.2955438494682312</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.205396980047226</c:v>
+                  <c:v>0.2052879333496094</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.2018556594848633</c:v>
+                  <c:v>0.2017484903335571</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.1965436637401581</c:v>
+                  <c:v>0.1964393109083176</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.1646717190742493</c:v>
+                  <c:v>0.164584293961525</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.1558184027671814</c:v>
+                  <c:v>0.1557356715202332</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.1097811460494995</c:v>
+                  <c:v>0.1097228601574898</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.09738650172948837</c:v>
+                  <c:v>0.09733479470014572</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.0885331854224205</c:v>
+                  <c:v>0.08848617970943451</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.05489057302474976</c:v>
+                  <c:v>0.05486143007874489</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.04957858100533485</c:v>
+                  <c:v>0.04955225810408592</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.04780791699886322</c:v>
+                  <c:v>0.0477825365960598</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.04426659271121025</c:v>
+                  <c:v>0.04424308985471726</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.04426659271121025</c:v>
+                  <c:v>0.04424308985471726</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.04249592870473862</c:v>
+                  <c:v>0.04247336462140083</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.03541327267885208</c:v>
+                  <c:v>0.03539447113871574</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.03364260867238045</c:v>
+                  <c:v>0.03362474963068962</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.03187194466590881</c:v>
+                  <c:v>0.0318550243973732</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.03187194466590881</c:v>
+                  <c:v>0.0318550243973732</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.0283306185156107</c:v>
+                  <c:v>0.02831557765603066</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.02655995450913906</c:v>
+                  <c:v>0.02654585428535938</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.02655995450913906</c:v>
+                  <c:v>0.02654585428535938</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.02478929050266743</c:v>
+                  <c:v>0.02477612905204296</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.02478929050266743</c:v>
+                  <c:v>0.02477612905204296</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.02478929050266743</c:v>
+                  <c:v>0.02477612905204296</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.02478929050266743</c:v>
+                  <c:v>0.02477612905204296</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.02478929050266743</c:v>
+                  <c:v>0.02477612905204296</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.02301862649619579</c:v>
+                  <c:v>0.02300640568137169</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.01593597233295441</c:v>
+                  <c:v>0.0159275121986866</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.00885331816971302</c:v>
+                  <c:v>0.008848617784678936</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.007082654628902674</c:v>
+                  <c:v>0.007078894414007664</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.007082654628902674</c:v>
+                  <c:v>0.007078894414007664</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.003541327314451337</c:v>
+                  <c:v>0.003539447207003832</c:v>
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>0</c:v>
@@ -1042,10 +1042,10 @@
         <v>11185</v>
       </c>
       <c r="D3" s="1">
-        <v>108036</v>
+        <v>108096</v>
       </c>
       <c r="E3" s="1">
-        <v>32024</v>
+        <v>32084</v>
       </c>
       <c r="F3" s="1">
         <v>75751</v>
@@ -1169,16 +1169,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>95.647705078125</v>
+        <v>95.65001678466797</v>
       </c>
       <c r="C3" s="1">
-        <v>108036</v>
+        <v>108096</v>
       </c>
       <c r="D3" s="1">
         <v>11185</v>
       </c>
       <c r="E3" s="1">
-        <v>32024</v>
+        <v>32084</v>
       </c>
       <c r="F3" s="1">
         <v>75751</v>
@@ -1195,7 +1195,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2">
-        <v>1.791911602020264</v>
+        <v>1.790960192680359</v>
       </c>
       <c r="C4" s="1">
         <v>2024</v>
@@ -1221,7 +1221,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2">
-        <v>0.3576740622520447</v>
+        <v>0.3574841618537903</v>
       </c>
       <c r="C5" s="1">
         <v>404</v>
@@ -1247,7 +1247,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>0.2957008183002472</v>
+        <v>0.2955438494682312</v>
       </c>
       <c r="C6" s="1">
         <v>334</v>
@@ -1273,7 +1273,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>0.205396980047226</v>
+        <v>0.2052879333496094</v>
       </c>
       <c r="C7" s="1">
         <v>232</v>
@@ -1299,7 +1299,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>0.2018556594848633</v>
+        <v>0.2017484903335571</v>
       </c>
       <c r="C8" s="1">
         <v>228</v>
@@ -1325,7 +1325,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>0.1965436637401581</v>
+        <v>0.1964393109083176</v>
       </c>
       <c r="C9" s="1">
         <v>222</v>
@@ -1351,7 +1351,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0.1646717190742493</v>
+        <v>0.164584293961525</v>
       </c>
       <c r="C10" s="1">
         <v>186</v>
@@ -1377,7 +1377,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0.1558184027671814</v>
+        <v>0.1557356715202332</v>
       </c>
       <c r="C11" s="1">
         <v>176</v>
@@ -1403,7 +1403,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.1097811460494995</v>
+        <v>0.1097228601574898</v>
       </c>
       <c r="C12" s="1">
         <v>124</v>
@@ -1429,7 +1429,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.09738650172948837</v>
+        <v>0.09733479470014572</v>
       </c>
       <c r="C13" s="1">
         <v>110</v>
@@ -1455,7 +1455,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.0885331854224205</v>
+        <v>0.08848617970943451</v>
       </c>
       <c r="C14" s="1">
         <v>100</v>
@@ -1481,7 +1481,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.05489057302474976</v>
+        <v>0.05486143007874489</v>
       </c>
       <c r="C15" s="1">
         <v>62</v>
@@ -1507,7 +1507,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.04957858100533485</v>
+        <v>0.04955225810408592</v>
       </c>
       <c r="C16" s="1">
         <v>56</v>
@@ -1533,7 +1533,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.04780791699886322</v>
+        <v>0.0477825365960598</v>
       </c>
       <c r="C17" s="1">
         <v>54</v>
@@ -1559,7 +1559,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.04426659271121025</v>
+        <v>0.04424308985471726</v>
       </c>
       <c r="C18" s="1">
         <v>50</v>
@@ -1585,7 +1585,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.04426659271121025</v>
+        <v>0.04424308985471726</v>
       </c>
       <c r="C19" s="1">
         <v>50</v>
@@ -1611,7 +1611,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.04249592870473862</v>
+        <v>0.04247336462140083</v>
       </c>
       <c r="C20" s="1">
         <v>48</v>
@@ -1637,7 +1637,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.03541327267885208</v>
+        <v>0.03539447113871574</v>
       </c>
       <c r="C21" s="1">
         <v>40</v>
@@ -1663,7 +1663,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.03364260867238045</v>
+        <v>0.03362474963068962</v>
       </c>
       <c r="C22" s="1">
         <v>38</v>
@@ -1689,7 +1689,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>0.03187194466590881</v>
+        <v>0.0318550243973732</v>
       </c>
       <c r="C23" s="1">
         <v>36</v>
@@ -1715,7 +1715,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>0.03187194466590881</v>
+        <v>0.0318550243973732</v>
       </c>
       <c r="C24" s="1">
         <v>36</v>
@@ -1741,7 +1741,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="2">
-        <v>0.0283306185156107</v>
+        <v>0.02831557765603066</v>
       </c>
       <c r="C25" s="1">
         <v>32</v>
@@ -1767,7 +1767,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="2">
-        <v>0.02655995450913906</v>
+        <v>0.02654585428535938</v>
       </c>
       <c r="C26" s="1">
         <v>30</v>
@@ -1793,7 +1793,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2">
-        <v>0.02655995450913906</v>
+        <v>0.02654585428535938</v>
       </c>
       <c r="C27" s="1">
         <v>30</v>
@@ -1819,7 +1819,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="2">
-        <v>0.02478929050266743</v>
+        <v>0.02477612905204296</v>
       </c>
       <c r="C28" s="1">
         <v>28</v>
@@ -1845,7 +1845,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="2">
-        <v>0.02478929050266743</v>
+        <v>0.02477612905204296</v>
       </c>
       <c r="C29" s="1">
         <v>28</v>
@@ -1871,7 +1871,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="2">
-        <v>0.02478929050266743</v>
+        <v>0.02477612905204296</v>
       </c>
       <c r="C30" s="1">
         <v>28</v>
@@ -1897,7 +1897,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="2">
-        <v>0.02478929050266743</v>
+        <v>0.02477612905204296</v>
       </c>
       <c r="C31" s="1">
         <v>28</v>
@@ -1923,7 +1923,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="2">
-        <v>0.02478929050266743</v>
+        <v>0.02477612905204296</v>
       </c>
       <c r="C32" s="1">
         <v>28</v>
@@ -1949,7 +1949,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="2">
-        <v>0.02301862649619579</v>
+        <v>0.02300640568137169</v>
       </c>
       <c r="C33" s="1">
         <v>26</v>
@@ -1975,7 +1975,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="2">
-        <v>0.01593597233295441</v>
+        <v>0.0159275121986866</v>
       </c>
       <c r="C34" s="1">
         <v>18</v>
@@ -2001,7 +2001,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="2">
-        <v>0.00885331816971302</v>
+        <v>0.008848617784678936</v>
       </c>
       <c r="C35" s="1">
         <v>10</v>
@@ -2027,7 +2027,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="2">
-        <v>0.007082654628902674</v>
+        <v>0.007078894414007664</v>
       </c>
       <c r="C36" s="1">
         <v>8</v>
@@ -2053,7 +2053,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="2">
-        <v>0.007082654628902674</v>
+        <v>0.007078894414007664</v>
       </c>
       <c r="C37" s="1">
         <v>8</v>
@@ -2079,7 +2079,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="2">
-        <v>0.003541327314451337</v>
+        <v>0.003539447207003832</v>
       </c>
       <c r="C38" s="1">
         <v>4</v>

--- a/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
+++ b/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
@@ -20,7 +20,7 @@
     <t>AT32F415RBT7_WorkBench</t>
   </si>
   <si>
-    <t>lto-llvm-b7239f.o</t>
+    <t>lto-llvm-dd7c40.o</t>
   </si>
   <si>
     <t>startup_at32f415.o</t>
@@ -249,7 +249,7 @@
               <c:strCache>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-b7239f.o</c:v>
+                  <c:v>lto-llvm-dd7c40.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>startup_at32f415.o</c:v>
@@ -344,7 +344,7 @@
               <c:strCache>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-b7239f.o</c:v>
+                  <c:v>lto-llvm-dd7c40.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>mf_w.l</c:v>
@@ -464,112 +464,112 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>95.65001678466797</c:v>
+                  <c:v>95.65025329589844</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.790960192680359</c:v>
+                  <c:v>1.790865182876587</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.3574841618537903</c:v>
+                  <c:v>0.3574651777744293</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.2955438494682312</c:v>
+                  <c:v>0.2955281436443329</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.2052879333496094</c:v>
+                  <c:v>0.2052770406007767</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.2017484903335571</c:v>
+                  <c:v>0.2017377763986588</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.1964393109083176</c:v>
+                  <c:v>0.1964288800954819</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.164584293961525</c:v>
+                  <c:v>0.1645755469799042</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.1557356715202332</c:v>
+                  <c:v>0.1557274013757706</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.1097228601574898</c:v>
+                  <c:v>0.109717033803463</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.09733479470014572</c:v>
+                  <c:v>0.09732963144779205</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.08848617970943451</c:v>
+                  <c:v>0.08848147839307785</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.05486143007874489</c:v>
+                  <c:v>0.05485851690173149</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.04955225810408592</c:v>
+                  <c:v>0.04954962804913521</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.0477825365960598</c:v>
+                  <c:v>0.04777999967336655</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.04424308985471726</c:v>
+                  <c:v>0.04424073919653893</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.04424308985471726</c:v>
+                  <c:v>0.04424073919653893</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.04247336462140083</c:v>
+                  <c:v>0.04247111082077026</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.03539447113871574</c:v>
+                  <c:v>0.03539259359240532</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.03362474963068962</c:v>
+                  <c:v>0.03362296149134636</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.0318550243973732</c:v>
+                  <c:v>0.0318533331155777</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.0318550243973732</c:v>
+                  <c:v>0.0318533331155777</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.02831557765603066</c:v>
+                  <c:v>0.02831407450139523</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.02654585428535938</c:v>
+                  <c:v>0.02654444426298142</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.02654585428535938</c:v>
+                  <c:v>0.02654444426298142</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.02477612905204296</c:v>
+                  <c:v>0.0247748140245676</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.02477612905204296</c:v>
+                  <c:v>0.0247748140245676</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.02477612905204296</c:v>
+                  <c:v>0.0247748140245676</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.02477612905204296</c:v>
+                  <c:v>0.0247748140245676</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.02477612905204296</c:v>
+                  <c:v>0.0247748140245676</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.02300640568137169</c:v>
+                  <c:v>0.02300518564879894</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.0159275121986866</c:v>
+                  <c:v>0.01592666655778885</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.008848617784678936</c:v>
+                  <c:v>0.00884814839810133</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.007078894414007664</c:v>
+                  <c:v>0.007078518625348806</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.007078894414007664</c:v>
+                  <c:v>0.007078518625348806</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.003539447207003832</c:v>
+                  <c:v>0.003539259312674403</c:v>
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>0</c:v>
@@ -1042,10 +1042,10 @@
         <v>11185</v>
       </c>
       <c r="D3" s="1">
-        <v>108096</v>
+        <v>108102</v>
       </c>
       <c r="E3" s="1">
-        <v>32084</v>
+        <v>32090</v>
       </c>
       <c r="F3" s="1">
         <v>75751</v>
@@ -1169,16 +1169,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>95.65001678466797</v>
+        <v>95.65025329589844</v>
       </c>
       <c r="C3" s="1">
-        <v>108096</v>
+        <v>108102</v>
       </c>
       <c r="D3" s="1">
         <v>11185</v>
       </c>
       <c r="E3" s="1">
-        <v>32084</v>
+        <v>32090</v>
       </c>
       <c r="F3" s="1">
         <v>75751</v>
@@ -1195,7 +1195,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2">
-        <v>1.790960192680359</v>
+        <v>1.790865182876587</v>
       </c>
       <c r="C4" s="1">
         <v>2024</v>
@@ -1221,7 +1221,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2">
-        <v>0.3574841618537903</v>
+        <v>0.3574651777744293</v>
       </c>
       <c r="C5" s="1">
         <v>404</v>
@@ -1247,7 +1247,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>0.2955438494682312</v>
+        <v>0.2955281436443329</v>
       </c>
       <c r="C6" s="1">
         <v>334</v>
@@ -1273,7 +1273,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>0.2052879333496094</v>
+        <v>0.2052770406007767</v>
       </c>
       <c r="C7" s="1">
         <v>232</v>
@@ -1299,7 +1299,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>0.2017484903335571</v>
+        <v>0.2017377763986588</v>
       </c>
       <c r="C8" s="1">
         <v>228</v>
@@ -1325,7 +1325,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>0.1964393109083176</v>
+        <v>0.1964288800954819</v>
       </c>
       <c r="C9" s="1">
         <v>222</v>
@@ -1351,7 +1351,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0.164584293961525</v>
+        <v>0.1645755469799042</v>
       </c>
       <c r="C10" s="1">
         <v>186</v>
@@ -1377,7 +1377,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0.1557356715202332</v>
+        <v>0.1557274013757706</v>
       </c>
       <c r="C11" s="1">
         <v>176</v>
@@ -1403,7 +1403,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.1097228601574898</v>
+        <v>0.109717033803463</v>
       </c>
       <c r="C12" s="1">
         <v>124</v>
@@ -1429,7 +1429,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.09733479470014572</v>
+        <v>0.09732963144779205</v>
       </c>
       <c r="C13" s="1">
         <v>110</v>
@@ -1455,7 +1455,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.08848617970943451</v>
+        <v>0.08848147839307785</v>
       </c>
       <c r="C14" s="1">
         <v>100</v>
@@ -1481,7 +1481,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.05486143007874489</v>
+        <v>0.05485851690173149</v>
       </c>
       <c r="C15" s="1">
         <v>62</v>
@@ -1507,7 +1507,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.04955225810408592</v>
+        <v>0.04954962804913521</v>
       </c>
       <c r="C16" s="1">
         <v>56</v>
@@ -1533,7 +1533,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.0477825365960598</v>
+        <v>0.04777999967336655</v>
       </c>
       <c r="C17" s="1">
         <v>54</v>
@@ -1559,7 +1559,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.04424308985471726</v>
+        <v>0.04424073919653893</v>
       </c>
       <c r="C18" s="1">
         <v>50</v>
@@ -1585,7 +1585,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.04424308985471726</v>
+        <v>0.04424073919653893</v>
       </c>
       <c r="C19" s="1">
         <v>50</v>
@@ -1611,7 +1611,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.04247336462140083</v>
+        <v>0.04247111082077026</v>
       </c>
       <c r="C20" s="1">
         <v>48</v>
@@ -1637,7 +1637,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.03539447113871574</v>
+        <v>0.03539259359240532</v>
       </c>
       <c r="C21" s="1">
         <v>40</v>
@@ -1663,7 +1663,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.03362474963068962</v>
+        <v>0.03362296149134636</v>
       </c>
       <c r="C22" s="1">
         <v>38</v>
@@ -1689,7 +1689,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>0.0318550243973732</v>
+        <v>0.0318533331155777</v>
       </c>
       <c r="C23" s="1">
         <v>36</v>
@@ -1715,7 +1715,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>0.0318550243973732</v>
+        <v>0.0318533331155777</v>
       </c>
       <c r="C24" s="1">
         <v>36</v>
@@ -1741,7 +1741,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="2">
-        <v>0.02831557765603066</v>
+        <v>0.02831407450139523</v>
       </c>
       <c r="C25" s="1">
         <v>32</v>
@@ -1767,7 +1767,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="2">
-        <v>0.02654585428535938</v>
+        <v>0.02654444426298142</v>
       </c>
       <c r="C26" s="1">
         <v>30</v>
@@ -1793,7 +1793,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2">
-        <v>0.02654585428535938</v>
+        <v>0.02654444426298142</v>
       </c>
       <c r="C27" s="1">
         <v>30</v>
@@ -1819,7 +1819,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="2">
-        <v>0.02477612905204296</v>
+        <v>0.0247748140245676</v>
       </c>
       <c r="C28" s="1">
         <v>28</v>
@@ -1845,7 +1845,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="2">
-        <v>0.02477612905204296</v>
+        <v>0.0247748140245676</v>
       </c>
       <c r="C29" s="1">
         <v>28</v>
@@ -1871,7 +1871,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="2">
-        <v>0.02477612905204296</v>
+        <v>0.0247748140245676</v>
       </c>
       <c r="C30" s="1">
         <v>28</v>
@@ -1897,7 +1897,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="2">
-        <v>0.02477612905204296</v>
+        <v>0.0247748140245676</v>
       </c>
       <c r="C31" s="1">
         <v>28</v>
@@ -1923,7 +1923,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="2">
-        <v>0.02477612905204296</v>
+        <v>0.0247748140245676</v>
       </c>
       <c r="C32" s="1">
         <v>28</v>
@@ -1949,7 +1949,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="2">
-        <v>0.02300640568137169</v>
+        <v>0.02300518564879894</v>
       </c>
       <c r="C33" s="1">
         <v>26</v>
@@ -1975,7 +1975,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="2">
-        <v>0.0159275121986866</v>
+        <v>0.01592666655778885</v>
       </c>
       <c r="C34" s="1">
         <v>18</v>
@@ -2001,7 +2001,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="2">
-        <v>0.008848617784678936</v>
+        <v>0.00884814839810133</v>
       </c>
       <c r="C35" s="1">
         <v>10</v>
@@ -2027,7 +2027,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="2">
-        <v>0.007078894414007664</v>
+        <v>0.007078518625348806</v>
       </c>
       <c r="C36" s="1">
         <v>8</v>
@@ -2053,7 +2053,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="2">
-        <v>0.007078894414007664</v>
+        <v>0.007078518625348806</v>
       </c>
       <c r="C37" s="1">
         <v>8</v>
@@ -2079,7 +2079,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="2">
-        <v>0.003539447207003832</v>
+        <v>0.003539259312674403</v>
       </c>
       <c r="C38" s="1">
         <v>4</v>

--- a/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
+++ b/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
@@ -20,7 +20,7 @@
     <t>AT32F415RBT7_WorkBench</t>
   </si>
   <si>
-    <t>lto-llvm-dd7c40.o</t>
+    <t>lto-llvm-b775ff.o</t>
   </si>
   <si>
     <t>startup_at32f415.o</t>
@@ -249,7 +249,7 @@
               <c:strCache>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-dd7c40.o</c:v>
+                  <c:v>lto-llvm-b775ff.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>startup_at32f415.o</c:v>
@@ -344,7 +344,7 @@
               <c:strCache>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-dd7c40.o</c:v>
+                  <c:v>lto-llvm-b775ff.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>mf_w.l</c:v>
@@ -464,112 +464,112 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>95.65025329589844</c:v>
+                  <c:v>95.64971160888672</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.790865182876587</c:v>
+                  <c:v>1.791087031364441</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.3574651777744293</c:v>
+                  <c:v>0.3575094640254974</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.2955281436443329</c:v>
+                  <c:v>0.2955647706985474</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.2052770406007767</c:v>
+                  <c:v>0.2053024619817734</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.2017377763986588</c:v>
+                  <c:v>0.2017627656459808</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.1964288800954819</c:v>
+                  <c:v>0.1964532285928726</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.1645755469799042</c:v>
+                  <c:v>0.1645959466695786</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.1557274013757706</c:v>
+                  <c:v>0.1557466983795166</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.109717033803463</c:v>
+                  <c:v>0.1097306311130524</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.09732963144779205</c:v>
+                  <c:v>0.09734168648719788</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.08848147839307785</c:v>
+                  <c:v>0.08849244564771652</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.05485851690173149</c:v>
+                  <c:v>0.05486531555652618</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.04954962804913521</c:v>
+                  <c:v>0.04955576732754707</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.04777999967336655</c:v>
+                  <c:v>0.0477859191596508</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.04424073919653893</c:v>
+                  <c:v>0.04424622282385826</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.04424073919653893</c:v>
+                  <c:v>0.04424622282385826</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.04247111082077026</c:v>
+                  <c:v>0.04247637093067169</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.03539259359240532</c:v>
+                  <c:v>0.03539697825908661</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.03362296149134636</c:v>
+                  <c:v>0.03362713009119034</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.0318533331155777</c:v>
+                  <c:v>0.03185727819800377</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.0318533331155777</c:v>
+                  <c:v>0.03185727819800377</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.02831407450139523</c:v>
+                  <c:v>0.02831758186221123</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.02654444426298142</c:v>
+                  <c:v>0.02654773369431496</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.02654444426298142</c:v>
+                  <c:v>0.02654773369431496</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.0247748140245676</c:v>
+                  <c:v>0.02477788366377354</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.0247748140245676</c:v>
+                  <c:v>0.02477788366377354</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.0247748140245676</c:v>
+                  <c:v>0.02477788366377354</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.0247748140245676</c:v>
+                  <c:v>0.02477788366377354</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.0247748140245676</c:v>
+                  <c:v>0.02477788366377354</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.02300518564879894</c:v>
+                  <c:v>0.02300803549587727</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.01592666655778885</c:v>
+                  <c:v>0.01592863909900188</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.00884814839810133</c:v>
+                  <c:v>0.008849244564771652</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.007078518625348806</c:v>
+                  <c:v>0.007079395465552807</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.007078518625348806</c:v>
+                  <c:v>0.007079395465552807</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.003539259312674403</c:v>
+                  <c:v>0.003539697732776403</c:v>
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>0</c:v>
@@ -1042,10 +1042,10 @@
         <v>11185</v>
       </c>
       <c r="D3" s="1">
-        <v>108102</v>
+        <v>108088</v>
       </c>
       <c r="E3" s="1">
-        <v>32090</v>
+        <v>32076</v>
       </c>
       <c r="F3" s="1">
         <v>75751</v>
@@ -1169,16 +1169,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>95.65025329589844</v>
+        <v>95.64971160888672</v>
       </c>
       <c r="C3" s="1">
-        <v>108102</v>
+        <v>108088</v>
       </c>
       <c r="D3" s="1">
         <v>11185</v>
       </c>
       <c r="E3" s="1">
-        <v>32090</v>
+        <v>32076</v>
       </c>
       <c r="F3" s="1">
         <v>75751</v>
@@ -1195,7 +1195,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2">
-        <v>1.790865182876587</v>
+        <v>1.791087031364441</v>
       </c>
       <c r="C4" s="1">
         <v>2024</v>
@@ -1221,7 +1221,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2">
-        <v>0.3574651777744293</v>
+        <v>0.3575094640254974</v>
       </c>
       <c r="C5" s="1">
         <v>404</v>
@@ -1247,7 +1247,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>0.2955281436443329</v>
+        <v>0.2955647706985474</v>
       </c>
       <c r="C6" s="1">
         <v>334</v>
@@ -1273,7 +1273,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>0.2052770406007767</v>
+        <v>0.2053024619817734</v>
       </c>
       <c r="C7" s="1">
         <v>232</v>
@@ -1299,7 +1299,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>0.2017377763986588</v>
+        <v>0.2017627656459808</v>
       </c>
       <c r="C8" s="1">
         <v>228</v>
@@ -1325,7 +1325,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>0.1964288800954819</v>
+        <v>0.1964532285928726</v>
       </c>
       <c r="C9" s="1">
         <v>222</v>
@@ -1351,7 +1351,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0.1645755469799042</v>
+        <v>0.1645959466695786</v>
       </c>
       <c r="C10" s="1">
         <v>186</v>
@@ -1377,7 +1377,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0.1557274013757706</v>
+        <v>0.1557466983795166</v>
       </c>
       <c r="C11" s="1">
         <v>176</v>
@@ -1403,7 +1403,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.109717033803463</v>
+        <v>0.1097306311130524</v>
       </c>
       <c r="C12" s="1">
         <v>124</v>
@@ -1429,7 +1429,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.09732963144779205</v>
+        <v>0.09734168648719788</v>
       </c>
       <c r="C13" s="1">
         <v>110</v>
@@ -1455,7 +1455,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.08848147839307785</v>
+        <v>0.08849244564771652</v>
       </c>
       <c r="C14" s="1">
         <v>100</v>
@@ -1481,7 +1481,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.05485851690173149</v>
+        <v>0.05486531555652618</v>
       </c>
       <c r="C15" s="1">
         <v>62</v>
@@ -1507,7 +1507,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.04954962804913521</v>
+        <v>0.04955576732754707</v>
       </c>
       <c r="C16" s="1">
         <v>56</v>
@@ -1533,7 +1533,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.04777999967336655</v>
+        <v>0.0477859191596508</v>
       </c>
       <c r="C17" s="1">
         <v>54</v>
@@ -1559,7 +1559,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.04424073919653893</v>
+        <v>0.04424622282385826</v>
       </c>
       <c r="C18" s="1">
         <v>50</v>
@@ -1585,7 +1585,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.04424073919653893</v>
+        <v>0.04424622282385826</v>
       </c>
       <c r="C19" s="1">
         <v>50</v>
@@ -1611,7 +1611,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.04247111082077026</v>
+        <v>0.04247637093067169</v>
       </c>
       <c r="C20" s="1">
         <v>48</v>
@@ -1637,7 +1637,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.03539259359240532</v>
+        <v>0.03539697825908661</v>
       </c>
       <c r="C21" s="1">
         <v>40</v>
@@ -1663,7 +1663,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.03362296149134636</v>
+        <v>0.03362713009119034</v>
       </c>
       <c r="C22" s="1">
         <v>38</v>
@@ -1689,7 +1689,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>0.0318533331155777</v>
+        <v>0.03185727819800377</v>
       </c>
       <c r="C23" s="1">
         <v>36</v>
@@ -1715,7 +1715,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>0.0318533331155777</v>
+        <v>0.03185727819800377</v>
       </c>
       <c r="C24" s="1">
         <v>36</v>
@@ -1741,7 +1741,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="2">
-        <v>0.02831407450139523</v>
+        <v>0.02831758186221123</v>
       </c>
       <c r="C25" s="1">
         <v>32</v>
@@ -1767,7 +1767,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="2">
-        <v>0.02654444426298142</v>
+        <v>0.02654773369431496</v>
       </c>
       <c r="C26" s="1">
         <v>30</v>
@@ -1793,7 +1793,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2">
-        <v>0.02654444426298142</v>
+        <v>0.02654773369431496</v>
       </c>
       <c r="C27" s="1">
         <v>30</v>
@@ -1819,7 +1819,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="2">
-        <v>0.0247748140245676</v>
+        <v>0.02477788366377354</v>
       </c>
       <c r="C28" s="1">
         <v>28</v>
@@ -1845,7 +1845,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="2">
-        <v>0.0247748140245676</v>
+        <v>0.02477788366377354</v>
       </c>
       <c r="C29" s="1">
         <v>28</v>
@@ -1871,7 +1871,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="2">
-        <v>0.0247748140245676</v>
+        <v>0.02477788366377354</v>
       </c>
       <c r="C30" s="1">
         <v>28</v>
@@ -1897,7 +1897,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="2">
-        <v>0.0247748140245676</v>
+        <v>0.02477788366377354</v>
       </c>
       <c r="C31" s="1">
         <v>28</v>
@@ -1923,7 +1923,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="2">
-        <v>0.0247748140245676</v>
+        <v>0.02477788366377354</v>
       </c>
       <c r="C32" s="1">
         <v>28</v>
@@ -1949,7 +1949,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="2">
-        <v>0.02300518564879894</v>
+        <v>0.02300803549587727</v>
       </c>
       <c r="C33" s="1">
         <v>26</v>
@@ -1975,7 +1975,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="2">
-        <v>0.01592666655778885</v>
+        <v>0.01592863909900188</v>
       </c>
       <c r="C34" s="1">
         <v>18</v>
@@ -2001,7 +2001,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="2">
-        <v>0.00884814839810133</v>
+        <v>0.008849244564771652</v>
       </c>
       <c r="C35" s="1">
         <v>10</v>
@@ -2027,7 +2027,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="2">
-        <v>0.007078518625348806</v>
+        <v>0.007079395465552807</v>
       </c>
       <c r="C36" s="1">
         <v>8</v>
@@ -2053,7 +2053,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="2">
-        <v>0.007078518625348806</v>
+        <v>0.007079395465552807</v>
       </c>
       <c r="C37" s="1">
         <v>8</v>
@@ -2079,7 +2079,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="2">
-        <v>0.003539259312674403</v>
+        <v>0.003539697732776403</v>
       </c>
       <c r="C38" s="1">
         <v>4</v>

--- a/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
+++ b/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
@@ -20,7 +20,7 @@
     <t>AT32F415RBT7_WorkBench</t>
   </si>
   <si>
-    <t>lto-llvm-b775ff.o</t>
+    <t>lto-llvm-8b3d02.o</t>
   </si>
   <si>
     <t>startup_at32f415.o</t>
@@ -249,7 +249,7 @@
               <c:strCache>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-b775ff.o</c:v>
+                  <c:v>lto-llvm-8b3d02.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>startup_at32f415.o</c:v>
@@ -344,7 +344,7 @@
               <c:strCache>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-b775ff.o</c:v>
+                  <c:v>lto-llvm-8b3d02.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>mf_w.l</c:v>
@@ -464,112 +464,112 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>95.64971160888672</c:v>
+                  <c:v>95.65509796142578</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.791087031364441</c:v>
+                  <c:v>1.788870811462402</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.3575094640254974</c:v>
+                  <c:v>0.3570671081542969</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.2955647706985474</c:v>
+                  <c:v>0.2951990365982056</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.2053024619817734</c:v>
+                  <c:v>0.2050484269857407</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.2017627656459808</c:v>
+                  <c:v>0.2015131115913391</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.1964532285928726</c:v>
+                  <c:v>0.1962101459503174</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.1645959466695786</c:v>
+                  <c:v>0.164392277598381</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.1557466983795166</c:v>
+                  <c:v>0.1555539816617966</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.1097306311130524</c:v>
+                  <c:v>0.109594851732254</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.09734168648719788</c:v>
+                  <c:v>0.09722124040126801</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.08849244564771652</c:v>
+                  <c:v>0.08838294446468353</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.05486531555652618</c:v>
+                  <c:v>0.05479742586612701</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.04955576732754707</c:v>
+                  <c:v>0.04949444904923439</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.0477859191596508</c:v>
+                  <c:v>0.04772679135203362</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.04424622282385826</c:v>
+                  <c:v>0.04419147223234177</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.04424622282385826</c:v>
+                  <c:v>0.04419147223234177</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.04247637093067169</c:v>
+                  <c:v>0.04242381453514099</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.03539697825908661</c:v>
+                  <c:v>0.03535318002104759</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.03362713009119034</c:v>
+                  <c:v>0.03358551859855652</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.03185727819800377</c:v>
+                  <c:v>0.03181786090135574</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.03185727819800377</c:v>
+                  <c:v>0.03181786090135574</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.02831758186221123</c:v>
+                  <c:v>0.0282825417816639</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.02654773369431496</c:v>
+                  <c:v>0.02651488408446312</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.02654773369431496</c:v>
+                  <c:v>0.02651488408446312</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.02477788366377354</c:v>
+                  <c:v>0.0247472245246172</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.02477788366377354</c:v>
+                  <c:v>0.0247472245246172</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.02477788366377354</c:v>
+                  <c:v>0.0247472245246172</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.02477788366377354</c:v>
+                  <c:v>0.0247472245246172</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.02477788366377354</c:v>
+                  <c:v>0.0247472245246172</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.02300803549587727</c:v>
+                  <c:v>0.02297956496477127</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.01592863909900188</c:v>
+                  <c:v>0.01590893045067787</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.008849244564771652</c:v>
+                  <c:v>0.008838295005261898</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.007079395465552807</c:v>
+                  <c:v>0.007070635445415974</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.007079395465552807</c:v>
+                  <c:v>0.007070635445415974</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.003539697732776403</c:v>
+                  <c:v>0.003535317722707987</c:v>
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>0</c:v>
@@ -1042,10 +1042,10 @@
         <v>11185</v>
       </c>
       <c r="D3" s="1">
-        <v>108088</v>
+        <v>108228</v>
       </c>
       <c r="E3" s="1">
-        <v>32076</v>
+        <v>32216</v>
       </c>
       <c r="F3" s="1">
         <v>75751</v>
@@ -1169,16 +1169,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>95.64971160888672</v>
+        <v>95.65509796142578</v>
       </c>
       <c r="C3" s="1">
-        <v>108088</v>
+        <v>108228</v>
       </c>
       <c r="D3" s="1">
         <v>11185</v>
       </c>
       <c r="E3" s="1">
-        <v>32076</v>
+        <v>32216</v>
       </c>
       <c r="F3" s="1">
         <v>75751</v>
@@ -1195,7 +1195,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2">
-        <v>1.791087031364441</v>
+        <v>1.788870811462402</v>
       </c>
       <c r="C4" s="1">
         <v>2024</v>
@@ -1221,7 +1221,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2">
-        <v>0.3575094640254974</v>
+        <v>0.3570671081542969</v>
       </c>
       <c r="C5" s="1">
         <v>404</v>
@@ -1247,7 +1247,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>0.2955647706985474</v>
+        <v>0.2951990365982056</v>
       </c>
       <c r="C6" s="1">
         <v>334</v>
@@ -1273,7 +1273,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>0.2053024619817734</v>
+        <v>0.2050484269857407</v>
       </c>
       <c r="C7" s="1">
         <v>232</v>
@@ -1299,7 +1299,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>0.2017627656459808</v>
+        <v>0.2015131115913391</v>
       </c>
       <c r="C8" s="1">
         <v>228</v>
@@ -1325,7 +1325,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>0.1964532285928726</v>
+        <v>0.1962101459503174</v>
       </c>
       <c r="C9" s="1">
         <v>222</v>
@@ -1351,7 +1351,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0.1645959466695786</v>
+        <v>0.164392277598381</v>
       </c>
       <c r="C10" s="1">
         <v>186</v>
@@ -1377,7 +1377,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0.1557466983795166</v>
+        <v>0.1555539816617966</v>
       </c>
       <c r="C11" s="1">
         <v>176</v>
@@ -1403,7 +1403,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.1097306311130524</v>
+        <v>0.109594851732254</v>
       </c>
       <c r="C12" s="1">
         <v>124</v>
@@ -1429,7 +1429,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.09734168648719788</v>
+        <v>0.09722124040126801</v>
       </c>
       <c r="C13" s="1">
         <v>110</v>
@@ -1455,7 +1455,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.08849244564771652</v>
+        <v>0.08838294446468353</v>
       </c>
       <c r="C14" s="1">
         <v>100</v>
@@ -1481,7 +1481,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.05486531555652618</v>
+        <v>0.05479742586612701</v>
       </c>
       <c r="C15" s="1">
         <v>62</v>
@@ -1507,7 +1507,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.04955576732754707</v>
+        <v>0.04949444904923439</v>
       </c>
       <c r="C16" s="1">
         <v>56</v>
@@ -1533,7 +1533,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.0477859191596508</v>
+        <v>0.04772679135203362</v>
       </c>
       <c r="C17" s="1">
         <v>54</v>
@@ -1559,7 +1559,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.04424622282385826</v>
+        <v>0.04419147223234177</v>
       </c>
       <c r="C18" s="1">
         <v>50</v>
@@ -1585,7 +1585,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.04424622282385826</v>
+        <v>0.04419147223234177</v>
       </c>
       <c r="C19" s="1">
         <v>50</v>
@@ -1611,7 +1611,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.04247637093067169</v>
+        <v>0.04242381453514099</v>
       </c>
       <c r="C20" s="1">
         <v>48</v>
@@ -1637,7 +1637,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.03539697825908661</v>
+        <v>0.03535318002104759</v>
       </c>
       <c r="C21" s="1">
         <v>40</v>
@@ -1663,7 +1663,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.03362713009119034</v>
+        <v>0.03358551859855652</v>
       </c>
       <c r="C22" s="1">
         <v>38</v>
@@ -1689,7 +1689,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>0.03185727819800377</v>
+        <v>0.03181786090135574</v>
       </c>
       <c r="C23" s="1">
         <v>36</v>
@@ -1715,7 +1715,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>0.03185727819800377</v>
+        <v>0.03181786090135574</v>
       </c>
       <c r="C24" s="1">
         <v>36</v>
@@ -1741,7 +1741,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="2">
-        <v>0.02831758186221123</v>
+        <v>0.0282825417816639</v>
       </c>
       <c r="C25" s="1">
         <v>32</v>
@@ -1767,7 +1767,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="2">
-        <v>0.02654773369431496</v>
+        <v>0.02651488408446312</v>
       </c>
       <c r="C26" s="1">
         <v>30</v>
@@ -1793,7 +1793,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2">
-        <v>0.02654773369431496</v>
+        <v>0.02651488408446312</v>
       </c>
       <c r="C27" s="1">
         <v>30</v>
@@ -1819,7 +1819,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="2">
-        <v>0.02477788366377354</v>
+        <v>0.0247472245246172</v>
       </c>
       <c r="C28" s="1">
         <v>28</v>
@@ -1845,7 +1845,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="2">
-        <v>0.02477788366377354</v>
+        <v>0.0247472245246172</v>
       </c>
       <c r="C29" s="1">
         <v>28</v>
@@ -1871,7 +1871,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="2">
-        <v>0.02477788366377354</v>
+        <v>0.0247472245246172</v>
       </c>
       <c r="C30" s="1">
         <v>28</v>
@@ -1897,7 +1897,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="2">
-        <v>0.02477788366377354</v>
+        <v>0.0247472245246172</v>
       </c>
       <c r="C31" s="1">
         <v>28</v>
@@ -1923,7 +1923,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="2">
-        <v>0.02477788366377354</v>
+        <v>0.0247472245246172</v>
       </c>
       <c r="C32" s="1">
         <v>28</v>
@@ -1949,7 +1949,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="2">
-        <v>0.02300803549587727</v>
+        <v>0.02297956496477127</v>
       </c>
       <c r="C33" s="1">
         <v>26</v>
@@ -1975,7 +1975,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="2">
-        <v>0.01592863909900188</v>
+        <v>0.01590893045067787</v>
       </c>
       <c r="C34" s="1">
         <v>18</v>
@@ -2001,7 +2001,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="2">
-        <v>0.008849244564771652</v>
+        <v>0.008838295005261898</v>
       </c>
       <c r="C35" s="1">
         <v>10</v>
@@ -2027,7 +2027,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="2">
-        <v>0.007079395465552807</v>
+        <v>0.007070635445415974</v>
       </c>
       <c r="C36" s="1">
         <v>8</v>
@@ -2053,7 +2053,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="2">
-        <v>0.007079395465552807</v>
+        <v>0.007070635445415974</v>
       </c>
       <c r="C37" s="1">
         <v>8</v>
@@ -2079,7 +2079,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="2">
-        <v>0.003539697732776403</v>
+        <v>0.003535317722707987</v>
       </c>
       <c r="C38" s="1">
         <v>4</v>

--- a/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
+++ b/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
@@ -20,7 +20,7 @@
     <t>AT32F415RBT7_WorkBench</t>
   </si>
   <si>
-    <t>lto-llvm-8b3d02.o</t>
+    <t>lto-llvm-7df018.o</t>
   </si>
   <si>
     <t>startup_at32f415.o</t>
@@ -249,7 +249,7 @@
               <c:strCache>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-8b3d02.o</c:v>
+                  <c:v>lto-llvm-7df018.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>startup_at32f415.o</c:v>
@@ -344,7 +344,7 @@
               <c:strCache>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-8b3d02.o</c:v>
+                  <c:v>lto-llvm-7df018.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>mf_w.l</c:v>
@@ -464,112 +464,112 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>95.65509796142578</c:v>
+                  <c:v>95.65616607666016</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.788870811462402</c:v>
+                  <c:v>1.7884281873703</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.3570671081542969</c:v>
+                  <c:v>0.3569787442684174</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.2951990365982056</c:v>
+                  <c:v>0.2951259911060333</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.2050484269857407</c:v>
+                  <c:v>0.2049977034330368</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.2015131115913391</c:v>
+                  <c:v>0.2014632523059845</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.1962101459503174</c:v>
+                  <c:v>0.1961615979671478</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.164392277598381</c:v>
+                  <c:v>0.164351612329483</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.1555539816617966</c:v>
+                  <c:v>0.1555154919624329</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.109594851732254</c:v>
+                  <c:v>0.1095677390694618</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.09722124040126801</c:v>
+                  <c:v>0.09719718992710114</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.08838294446468353</c:v>
+                  <c:v>0.08836107701063156</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.05479742586612701</c:v>
+                  <c:v>0.05478386953473091</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.04949444904923439</c:v>
+                  <c:v>0.04948220402002335</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.04772679135203362</c:v>
+                  <c:v>0.04771498218178749</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.04419147223234177</c:v>
+                  <c:v>0.04418053850531578</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.04419147223234177</c:v>
+                  <c:v>0.04418053850531578</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.04242381453514099</c:v>
+                  <c:v>0.04241331666707993</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.03535318002104759</c:v>
+                  <c:v>0.0353444330394268</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.03358551859855652</c:v>
+                  <c:v>0.03357721120119095</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.03181786090135574</c:v>
+                  <c:v>0.03180998936295509</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.03181786090135574</c:v>
+                  <c:v>0.03180998936295509</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.0282825417816639</c:v>
+                  <c:v>0.02827554568648338</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.02651488408446312</c:v>
+                  <c:v>0.02650832384824753</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.02651488408446312</c:v>
+                  <c:v>0.02650832384824753</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.0247472245246172</c:v>
+                  <c:v>0.02474110201001167</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.0247472245246172</c:v>
+                  <c:v>0.02474110201001167</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.0247472245246172</c:v>
+                  <c:v>0.02474110201001167</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.0247472245246172</c:v>
+                  <c:v>0.02474110201001167</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.0247472245246172</c:v>
+                  <c:v>0.02474110201001167</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.02297956496477127</c:v>
+                  <c:v>0.02297388017177582</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.01590893045067787</c:v>
+                  <c:v>0.01590499468147755</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.008838295005261898</c:v>
+                  <c:v>0.008836108259856701</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.007070635445415974</c:v>
+                  <c:v>0.007068886421620846</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.007070635445415974</c:v>
+                  <c:v>0.007068886421620846</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.003535317722707987</c:v>
+                  <c:v>0.003534443210810423</c:v>
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>0</c:v>
@@ -1042,10 +1042,10 @@
         <v>11185</v>
       </c>
       <c r="D3" s="1">
-        <v>108228</v>
+        <v>108256</v>
       </c>
       <c r="E3" s="1">
-        <v>32216</v>
+        <v>32244</v>
       </c>
       <c r="F3" s="1">
         <v>75751</v>
@@ -1169,16 +1169,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>95.65509796142578</v>
+        <v>95.65616607666016</v>
       </c>
       <c r="C3" s="1">
-        <v>108228</v>
+        <v>108256</v>
       </c>
       <c r="D3" s="1">
         <v>11185</v>
       </c>
       <c r="E3" s="1">
-        <v>32216</v>
+        <v>32244</v>
       </c>
       <c r="F3" s="1">
         <v>75751</v>
@@ -1195,7 +1195,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2">
-        <v>1.788870811462402</v>
+        <v>1.7884281873703</v>
       </c>
       <c r="C4" s="1">
         <v>2024</v>
@@ -1221,7 +1221,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2">
-        <v>0.3570671081542969</v>
+        <v>0.3569787442684174</v>
       </c>
       <c r="C5" s="1">
         <v>404</v>
@@ -1247,7 +1247,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>0.2951990365982056</v>
+        <v>0.2951259911060333</v>
       </c>
       <c r="C6" s="1">
         <v>334</v>
@@ -1273,7 +1273,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>0.2050484269857407</v>
+        <v>0.2049977034330368</v>
       </c>
       <c r="C7" s="1">
         <v>232</v>
@@ -1299,7 +1299,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>0.2015131115913391</v>
+        <v>0.2014632523059845</v>
       </c>
       <c r="C8" s="1">
         <v>228</v>
@@ -1325,7 +1325,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>0.1962101459503174</v>
+        <v>0.1961615979671478</v>
       </c>
       <c r="C9" s="1">
         <v>222</v>
@@ -1351,7 +1351,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0.164392277598381</v>
+        <v>0.164351612329483</v>
       </c>
       <c r="C10" s="1">
         <v>186</v>
@@ -1377,7 +1377,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0.1555539816617966</v>
+        <v>0.1555154919624329</v>
       </c>
       <c r="C11" s="1">
         <v>176</v>
@@ -1403,7 +1403,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.109594851732254</v>
+        <v>0.1095677390694618</v>
       </c>
       <c r="C12" s="1">
         <v>124</v>
@@ -1429,7 +1429,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.09722124040126801</v>
+        <v>0.09719718992710114</v>
       </c>
       <c r="C13" s="1">
         <v>110</v>
@@ -1455,7 +1455,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.08838294446468353</v>
+        <v>0.08836107701063156</v>
       </c>
       <c r="C14" s="1">
         <v>100</v>
@@ -1481,7 +1481,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.05479742586612701</v>
+        <v>0.05478386953473091</v>
       </c>
       <c r="C15" s="1">
         <v>62</v>
@@ -1507,7 +1507,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.04949444904923439</v>
+        <v>0.04948220402002335</v>
       </c>
       <c r="C16" s="1">
         <v>56</v>
@@ -1533,7 +1533,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.04772679135203362</v>
+        <v>0.04771498218178749</v>
       </c>
       <c r="C17" s="1">
         <v>54</v>
@@ -1559,7 +1559,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.04419147223234177</v>
+        <v>0.04418053850531578</v>
       </c>
       <c r="C18" s="1">
         <v>50</v>
@@ -1585,7 +1585,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.04419147223234177</v>
+        <v>0.04418053850531578</v>
       </c>
       <c r="C19" s="1">
         <v>50</v>
@@ -1611,7 +1611,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.04242381453514099</v>
+        <v>0.04241331666707993</v>
       </c>
       <c r="C20" s="1">
         <v>48</v>
@@ -1637,7 +1637,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.03535318002104759</v>
+        <v>0.0353444330394268</v>
       </c>
       <c r="C21" s="1">
         <v>40</v>
@@ -1663,7 +1663,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.03358551859855652</v>
+        <v>0.03357721120119095</v>
       </c>
       <c r="C22" s="1">
         <v>38</v>
@@ -1689,7 +1689,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>0.03181786090135574</v>
+        <v>0.03180998936295509</v>
       </c>
       <c r="C23" s="1">
         <v>36</v>
@@ -1715,7 +1715,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>0.03181786090135574</v>
+        <v>0.03180998936295509</v>
       </c>
       <c r="C24" s="1">
         <v>36</v>
@@ -1741,7 +1741,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="2">
-        <v>0.0282825417816639</v>
+        <v>0.02827554568648338</v>
       </c>
       <c r="C25" s="1">
         <v>32</v>
@@ -1767,7 +1767,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="2">
-        <v>0.02651488408446312</v>
+        <v>0.02650832384824753</v>
       </c>
       <c r="C26" s="1">
         <v>30</v>
@@ -1793,7 +1793,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2">
-        <v>0.02651488408446312</v>
+        <v>0.02650832384824753</v>
       </c>
       <c r="C27" s="1">
         <v>30</v>
@@ -1819,7 +1819,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="2">
-        <v>0.0247472245246172</v>
+        <v>0.02474110201001167</v>
       </c>
       <c r="C28" s="1">
         <v>28</v>
@@ -1845,7 +1845,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="2">
-        <v>0.0247472245246172</v>
+        <v>0.02474110201001167</v>
       </c>
       <c r="C29" s="1">
         <v>28</v>
@@ -1871,7 +1871,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="2">
-        <v>0.0247472245246172</v>
+        <v>0.02474110201001167</v>
       </c>
       <c r="C30" s="1">
         <v>28</v>
@@ -1897,7 +1897,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="2">
-        <v>0.0247472245246172</v>
+        <v>0.02474110201001167</v>
       </c>
       <c r="C31" s="1">
         <v>28</v>
@@ -1923,7 +1923,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="2">
-        <v>0.0247472245246172</v>
+        <v>0.02474110201001167</v>
       </c>
       <c r="C32" s="1">
         <v>28</v>
@@ -1949,7 +1949,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="2">
-        <v>0.02297956496477127</v>
+        <v>0.02297388017177582</v>
       </c>
       <c r="C33" s="1">
         <v>26</v>
@@ -1975,7 +1975,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="2">
-        <v>0.01590893045067787</v>
+        <v>0.01590499468147755</v>
       </c>
       <c r="C34" s="1">
         <v>18</v>
@@ -2001,7 +2001,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="2">
-        <v>0.008838295005261898</v>
+        <v>0.008836108259856701</v>
       </c>
       <c r="C35" s="1">
         <v>10</v>
@@ -2027,7 +2027,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="2">
-        <v>0.007070635445415974</v>
+        <v>0.007068886421620846</v>
       </c>
       <c r="C36" s="1">
         <v>8</v>
@@ -2053,7 +2053,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="2">
-        <v>0.007070635445415974</v>
+        <v>0.007068886421620846</v>
       </c>
       <c r="C37" s="1">
         <v>8</v>
@@ -2079,7 +2079,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="2">
-        <v>0.003535317722707987</v>
+        <v>0.003534443210810423</v>
       </c>
       <c r="C38" s="1">
         <v>4</v>

--- a/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
+++ b/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
@@ -20,7 +20,7 @@
     <t>AT32F415RBT7_WorkBench</t>
   </si>
   <si>
-    <t>lto-llvm-7df018.o</t>
+    <t>lto-llvm-8de445.o</t>
   </si>
   <si>
     <t>startup_at32f415.o</t>
@@ -249,7 +249,7 @@
               <c:strCache>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-7df018.o</c:v>
+                  <c:v>lto-llvm-8de445.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>startup_at32f415.o</c:v>
@@ -344,7 +344,7 @@
               <c:strCache>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-7df018.o</c:v>
+                  <c:v>lto-llvm-8de445.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>mf_w.l</c:v>
@@ -464,112 +464,112 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>95.65616607666016</c:v>
+                  <c:v>95.65824127197266</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.7884281873703</c:v>
+                  <c:v>1.787575244903565</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.3569787442684174</c:v>
+                  <c:v>0.3568085134029388</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.2951259911060333</c:v>
+                  <c:v>0.2949852645397186</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.2049977034330368</c:v>
+                  <c:v>0.204899936914444</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.2014632523059845</c:v>
+                  <c:v>0.2013671845197678</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.1961615979671478</c:v>
+                  <c:v>0.1960680335760117</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.164351612329483</c:v>
+                  <c:v>0.1642732173204422</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.1555154919624329</c:v>
+                  <c:v>0.1554413288831711</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.1095677390694618</c:v>
+                  <c:v>0.109515480697155</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.09719718992710114</c:v>
+                  <c:v>0.09715083241462708</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.08836107701063156</c:v>
+                  <c:v>0.08831893652677536</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.05478386953473091</c:v>
+                  <c:v>0.0547577403485775</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.04948220402002335</c:v>
+                  <c:v>0.04945860430598259</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.04771498218178749</c:v>
+                  <c:v>0.04769222438335419</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.04418053850531578</c:v>
+                  <c:v>0.04415946826338768</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.04418053850531578</c:v>
+                  <c:v>0.04415946826338768</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.04241331666707993</c:v>
+                  <c:v>0.04239308834075928</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.0353444330394268</c:v>
+                  <c:v>0.03532757610082626</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.03357721120119095</c:v>
+                  <c:v>0.03356119617819786</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.03180998936295509</c:v>
+                  <c:v>0.03179481625556946</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.03180998936295509</c:v>
+                  <c:v>0.03179481625556946</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.02827554568648338</c:v>
+                  <c:v>0.02826206013560295</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.02650832384824753</c:v>
+                  <c:v>0.0264956820756197</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.02650832384824753</c:v>
+                  <c:v>0.0264956820756197</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.02474110201001167</c:v>
+                  <c:v>0.0247293021529913</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.02474110201001167</c:v>
+                  <c:v>0.0247293021529913</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.02474110201001167</c:v>
+                  <c:v>0.0247293021529913</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.02474110201001167</c:v>
+                  <c:v>0.0247293021529913</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.02474110201001167</c:v>
+                  <c:v>0.0247293021529913</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.02297388017177582</c:v>
+                  <c:v>0.02296292409300804</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.01590499468147755</c:v>
+                  <c:v>0.01589740812778473</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.008836108259856701</c:v>
+                  <c:v>0.008831894025206566</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.007068886421620846</c:v>
+                  <c:v>0.007065515033900738</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.007068886421620846</c:v>
+                  <c:v>0.007065515033900738</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.003534443210810423</c:v>
+                  <c:v>0.003532757516950369</c:v>
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>0</c:v>
@@ -1042,10 +1042,10 @@
         <v>11185</v>
       </c>
       <c r="D3" s="1">
-        <v>108256</v>
+        <v>108310</v>
       </c>
       <c r="E3" s="1">
-        <v>32244</v>
+        <v>32298</v>
       </c>
       <c r="F3" s="1">
         <v>75751</v>
@@ -1169,16 +1169,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>95.65616607666016</v>
+        <v>95.65824127197266</v>
       </c>
       <c r="C3" s="1">
-        <v>108256</v>
+        <v>108310</v>
       </c>
       <c r="D3" s="1">
         <v>11185</v>
       </c>
       <c r="E3" s="1">
-        <v>32244</v>
+        <v>32298</v>
       </c>
       <c r="F3" s="1">
         <v>75751</v>
@@ -1195,7 +1195,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2">
-        <v>1.7884281873703</v>
+        <v>1.787575244903565</v>
       </c>
       <c r="C4" s="1">
         <v>2024</v>
@@ -1221,7 +1221,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2">
-        <v>0.3569787442684174</v>
+        <v>0.3568085134029388</v>
       </c>
       <c r="C5" s="1">
         <v>404</v>
@@ -1247,7 +1247,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>0.2951259911060333</v>
+        <v>0.2949852645397186</v>
       </c>
       <c r="C6" s="1">
         <v>334</v>
@@ -1273,7 +1273,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>0.2049977034330368</v>
+        <v>0.204899936914444</v>
       </c>
       <c r="C7" s="1">
         <v>232</v>
@@ -1299,7 +1299,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>0.2014632523059845</v>
+        <v>0.2013671845197678</v>
       </c>
       <c r="C8" s="1">
         <v>228</v>
@@ -1325,7 +1325,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>0.1961615979671478</v>
+        <v>0.1960680335760117</v>
       </c>
       <c r="C9" s="1">
         <v>222</v>
@@ -1351,7 +1351,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0.164351612329483</v>
+        <v>0.1642732173204422</v>
       </c>
       <c r="C10" s="1">
         <v>186</v>
@@ -1377,7 +1377,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0.1555154919624329</v>
+        <v>0.1554413288831711</v>
       </c>
       <c r="C11" s="1">
         <v>176</v>
@@ -1403,7 +1403,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.1095677390694618</v>
+        <v>0.109515480697155</v>
       </c>
       <c r="C12" s="1">
         <v>124</v>
@@ -1429,7 +1429,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.09719718992710114</v>
+        <v>0.09715083241462708</v>
       </c>
       <c r="C13" s="1">
         <v>110</v>
@@ -1455,7 +1455,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.08836107701063156</v>
+        <v>0.08831893652677536</v>
       </c>
       <c r="C14" s="1">
         <v>100</v>
@@ -1481,7 +1481,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.05478386953473091</v>
+        <v>0.0547577403485775</v>
       </c>
       <c r="C15" s="1">
         <v>62</v>
@@ -1507,7 +1507,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.04948220402002335</v>
+        <v>0.04945860430598259</v>
       </c>
       <c r="C16" s="1">
         <v>56</v>
@@ -1533,7 +1533,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.04771498218178749</v>
+        <v>0.04769222438335419</v>
       </c>
       <c r="C17" s="1">
         <v>54</v>
@@ -1559,7 +1559,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.04418053850531578</v>
+        <v>0.04415946826338768</v>
       </c>
       <c r="C18" s="1">
         <v>50</v>
@@ -1585,7 +1585,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.04418053850531578</v>
+        <v>0.04415946826338768</v>
       </c>
       <c r="C19" s="1">
         <v>50</v>
@@ -1611,7 +1611,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.04241331666707993</v>
+        <v>0.04239308834075928</v>
       </c>
       <c r="C20" s="1">
         <v>48</v>
@@ -1637,7 +1637,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.0353444330394268</v>
+        <v>0.03532757610082626</v>
       </c>
       <c r="C21" s="1">
         <v>40</v>
@@ -1663,7 +1663,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.03357721120119095</v>
+        <v>0.03356119617819786</v>
       </c>
       <c r="C22" s="1">
         <v>38</v>
@@ -1689,7 +1689,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>0.03180998936295509</v>
+        <v>0.03179481625556946</v>
       </c>
       <c r="C23" s="1">
         <v>36</v>
@@ -1715,7 +1715,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>0.03180998936295509</v>
+        <v>0.03179481625556946</v>
       </c>
       <c r="C24" s="1">
         <v>36</v>
@@ -1741,7 +1741,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="2">
-        <v>0.02827554568648338</v>
+        <v>0.02826206013560295</v>
       </c>
       <c r="C25" s="1">
         <v>32</v>
@@ -1767,7 +1767,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="2">
-        <v>0.02650832384824753</v>
+        <v>0.0264956820756197</v>
       </c>
       <c r="C26" s="1">
         <v>30</v>
@@ -1793,7 +1793,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2">
-        <v>0.02650832384824753</v>
+        <v>0.0264956820756197</v>
       </c>
       <c r="C27" s="1">
         <v>30</v>
@@ -1819,7 +1819,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="2">
-        <v>0.02474110201001167</v>
+        <v>0.0247293021529913</v>
       </c>
       <c r="C28" s="1">
         <v>28</v>
@@ -1845,7 +1845,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="2">
-        <v>0.02474110201001167</v>
+        <v>0.0247293021529913</v>
       </c>
       <c r="C29" s="1">
         <v>28</v>
@@ -1871,7 +1871,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="2">
-        <v>0.02474110201001167</v>
+        <v>0.0247293021529913</v>
       </c>
       <c r="C30" s="1">
         <v>28</v>
@@ -1897,7 +1897,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="2">
-        <v>0.02474110201001167</v>
+        <v>0.0247293021529913</v>
       </c>
       <c r="C31" s="1">
         <v>28</v>
@@ -1923,7 +1923,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="2">
-        <v>0.02474110201001167</v>
+        <v>0.0247293021529913</v>
       </c>
       <c r="C32" s="1">
         <v>28</v>
@@ -1949,7 +1949,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="2">
-        <v>0.02297388017177582</v>
+        <v>0.02296292409300804</v>
       </c>
       <c r="C33" s="1">
         <v>26</v>
@@ -1975,7 +1975,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="2">
-        <v>0.01590499468147755</v>
+        <v>0.01589740812778473</v>
       </c>
       <c r="C34" s="1">
         <v>18</v>
@@ -2001,7 +2001,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="2">
-        <v>0.008836108259856701</v>
+        <v>0.008831894025206566</v>
       </c>
       <c r="C35" s="1">
         <v>10</v>
@@ -2027,7 +2027,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="2">
-        <v>0.007068886421620846</v>
+        <v>0.007065515033900738</v>
       </c>
       <c r="C36" s="1">
         <v>8</v>
@@ -2053,7 +2053,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="2">
-        <v>0.007068886421620846</v>
+        <v>0.007065515033900738</v>
       </c>
       <c r="C37" s="1">
         <v>8</v>
@@ -2079,7 +2079,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="2">
-        <v>0.003534443210810423</v>
+        <v>0.003532757516950369</v>
       </c>
       <c r="C38" s="1">
         <v>4</v>

--- a/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
+++ b/app/project/MDK_V5/AT32F415RBT7_WorkBench_analysis.xlsx
@@ -20,7 +20,7 @@
     <t>AT32F415RBT7_WorkBench</t>
   </si>
   <si>
-    <t>lto-llvm-8de445.o</t>
+    <t>lto-llvm-678da1.o</t>
   </si>
   <si>
     <t>startup_at32f415.o</t>
@@ -249,7 +249,7 @@
               <c:strCache>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-8de445.o</c:v>
+                  <c:v>lto-llvm-678da1.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>startup_at32f415.o</c:v>
@@ -344,7 +344,7 @@
               <c:strCache>
                 <c:ptCount val="37"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-8de445.o</c:v>
+                  <c:v>lto-llvm-678da1.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>mf_w.l</c:v>
